--- a/stories/arbres/TREE-AUT-009.xlsx
+++ b/stories/arbres/TREE-AUT-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami est avec papa, dans le salon. Sami a envie de jouer. papa est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Sami écoute papa. Sami entend les mots : sac, ce que l'adulte a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la cuisine. On entend un oiseau. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers la cuisine. On entend un oiseau. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers la cuisine. On entend un oiseau. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le jardin. Ça sent le pain chaud. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le jardin. Ça sent le pain chaud. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le jardin. Ça sent le pain chaud. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la chambre. Le vent est doux. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers la chambre. Le vent est doux. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers la chambre. Le vent est doux. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-009.xlsx
+++ b/stories/arbres/TREE-AUT-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami est avec papa, dans le salon. Sami a envie de jouer. papa est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Sami écoute papa. Sami entend les mots : sac, ce que l'adulte a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Sami a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Sami a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Sami a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Sami a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Sami a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Sami rejoint le matin. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Sami a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Sami a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Sami rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Sami a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Sami a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Sami rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Sami rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Sami rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-009.xlsx
+++ b/stories/arbres/TREE-AUT-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Préparer son sac — dans le salon</t>
+          <t>Le sac bleu de Victorino</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le sac bleu de Victorino est vide sur le tapis. Papa a dit la gourde, le petit livre, le doudou. Victorino les met dans le sac, pièce après pièce.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sami est avec papa, dans le salon. Sami a envie de jouer. papa est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Sami écoute papa. Sami entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>Sur le crochet du salon, un sac bleu dort. Ses dents de fermeture brillent un peu. Un rayon glisse sur le tapis. Le tapis est doux, un peu rêche au bord. Ça sent le pain chaud. Une cuillère frappe un bol, tout près. Victorino, tu as entendu le bol ? Oui, maman. Le pain est encore tiède. Papa pose une gourde près du sac. Victorino, tu viens ? On prépare le sac ensemble. J'arrive, papa. En ce moment, Victorino s'assoit sur le tapis. Le sac bleu est ouvert. Il est encore vide. On met dans le sac ce que j'ai dit. La gourde. Le petit livre. Le doudou. Victorino écoute jusqu'au bout. Il touche la sangle, tout doucement. La gourde, le livre, le doudou. Bravo. Tu as bien écouté. Tu as fini d'écouter papa ? Oui, maman. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,31 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sami est avec papa, dans le salon. Sami a envie de jouer. papa est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Sami écoute papa. Sami entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>narrateur|Sur le crochet du salon, un sac bleu dort.
+narrateur|Ses dents de fermeture brillent un peu.
+narrateur|Un rayon glisse sur le tapis.
+narrateur|Le tapis est doux, un peu rêche au bord.
+narrateur|Ça sent le pain chaud.
+narrateur|Une cuillère frappe un bol, tout près.
+maman|Victorino, tu as entendu le bol ?
+enfant-m|Oui, maman.
+maman|Le pain est encore tiède.
+narrateur|Papa pose une gourde près du sac.
+papa|Victorino, tu viens ?
+papa|On prépare le sac ensemble.
+enfant-m|J'arrive, papa.
+narrateur|En ce moment, Victorino s'assoit sur le tapis.
+narrateur|Le sac bleu est ouvert.
+narrateur|Il est encore vide.
+papa|On met dans le sac ce que j'ai dit.
+papa|La gourde. Le petit livre. Le doudou.
+narrateur|Victorino écoute jusqu'au bout.
+narrateur|Il touche la sangle, tout doucement.
+enfant-m|La gourde, le livre, le doudou.
+papa|Bravo. Tu as bien écouté.
+maman|Tu as fini d'écouter papa ?
+enfant-m|Oui, maman.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1389,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Victorino peut aller dans la cuisine, dans le jardin, ou dans la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1553,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Victorino peut aller dans la cuisine, dans le jardin, ou dans la chambre.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la cuisine. On entend un oiseau. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Victorino prend le sac bleu par la sangle. Il va vers la cuisine. Le carrelage est frais sous les pieds. Ça sent encore le pain. Tu viens avec le sac ? Oui, maman. Le sac est avec moi. La gourde attend près du bol. Tu mets la gourde. C'est ce que j'ai dit. Victorino prend la gourde. Il la met dans le sac. Ça fait un petit bruit de plastique. Bravo. La gourde est dans le sac. Tu as mis ce que papa a dit ? Oui. La gourde. On continue. Tout doucement.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1721,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers la cuisine. On entend un oiseau. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On écoute jusqu'au bout.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Victorino prend le sac bleu par la sangle.
+narrateur|Il va vers la cuisine.
+narrateur|Le carrelage est frais sous les pieds.
+narrateur|Ça sent encore le pain.
+maman|Tu viens avec le sac ?
+enfant-m|Oui, maman. Le sac est avec moi.
+narrateur|La gourde attend près du bol.
+papa|Tu mets la gourde. C'est ce que j'ai dit.
+narrateur|Victorino prend la gourde.
+narrateur|Il la met dans le sac.
+narrateur|Ça fait un petit bruit de plastique.
+papa|Bravo. La gourde est dans le sac.
+maman|Tu as mis ce que papa a dit ?
+enfant-m|Oui. La gourde.
+maman|On continue. Tout doucement.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Victorino prépare le sac. Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1923,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Victorino prépare le sac.
+narrateur|Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>Victorino hoche la tête. Oui. On met dans le sac ce que l'adulte a dit. La gourde est dedans. Bravo. Tu as fait du bon travail. On continue avec papa ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2096,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>narrateur|Victorino hoche la tête.
+papa|Oui. On met dans le sac ce que l'adulte a dit.
+enfant-m|La gourde est dedans.
+maman|Bravo. Tu as fait du bon travail.
+maman|On continue avec papa ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2266,7 +2321,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>Sur le carrelage, des cubes attendent. Un cube rouge brille près du sac. Les cubes, papa ! Les cubes restent ici, près de nous. Dans le sac, on met ce que j'ai dit. Victorino pose un cube à sa place. Puis il pousse le petit livre dans le sac. Le livre va dans le sac ? Oui. C'est ce que papa a dit. Bravo. Tu ranges et tu prépares. Tu as fini le livre ? Il est dans le sac.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,7 +2461,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Sur le carrelage, des cubes attendent.
+narrateur|Un cube rouge brille près du sac.
+enfant-m|Les cubes, papa !
+papa|Les cubes restent ici, près de nous.
+papa|Dans le sac, on met ce que j'ai dit.
+narrateur|Victorino pose un cube à sa place.
+narrateur|Puis il pousse le petit livre dans le sac.
+maman|Le livre va dans le sac ?
+enfant-m|Oui. C'est ce que papa a dit.
+maman|Bravo. Tu ranges et tu prépares.
+papa|Tu as fini le livre ?
+enfant-m|Il est dans le sac.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2626,7 +2692,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, le carrelage est encore frais. Les cubes font toc, toc, tout bas. Un oiseau chante derrière la vitre. Victorino tire la fermeture du sac. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. La gourde, le livre, le doudou. Bravo. Tu as fait du bon travail. Le pain est encore tiède. Tu as faim ? Un peu, maman. Le sac bleu attend près de la chaise.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2832,18 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, le carrelage est encore frais.
+narrateur|Les cubes font toc, toc, tout bas.
+narrateur|Un oiseau chante derrière la vitre.
+narrateur|Victorino tire la fermeture du sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|La gourde, le livre, le doudou.
+maman|Bravo. Tu as fait du bon travail.
+maman|Le pain est encore tiède. Tu as faim ?
+enfant-m|Un peu, maman.
+narrateur|Le sac bleu attend près de la chaise.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2871,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis la gourde dans le sac. Bravo, Victorino. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3011,10 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis la gourde dans le sac.
+papa|Bravo, Victorino.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3042,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, la cuisine est calme. Le réfrigérateur fait un petit ronron. Les cubes sont en tas, sages. Victorino appuie sur la fermeture. Ça fait zzz, tout doux. Le sac est prêt. C'est ce que l'adulte a dit. Tout est dans le sac. Bravo, Victorino. Tu as bien dormi un peu ? Oui, maman. Une miette brille encore sur la table.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3182,18 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, la cuisine est calme.
+narrateur|Le réfrigérateur fait un petit ronron.
+narrateur|Les cubes sont en tas, sages.
+narrateur|Victorino appuie sur la fermeture.
+narrateur|Ça fait zzz, tout doux.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Tout est dans le sac.
+maman|Bravo, Victorino.
+maman|Tu as bien dormi un peu ?
+enfant-m|Oui, maman.
+narrateur|Une miette brille encore sur la table.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3221,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est fermé. Bravo. C'est du bon travail. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3361,10 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac est fermé.
+papa|Bravo. C'est du bon travail.
+maman|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3392,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe de la cuisine est allumée. Les cubes ont des ombres longues. Victorino ferme le sac, lentement. La fermeture fait zzz. Le sac est prêt pour demain. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. C'est du bon travail. Tu as fini de fermer le sac ? Oui, maman. Le sac bleu se pose près de la porte.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3532,17 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, la lampe de la cuisine est allumée.
+narrateur|Les cubes ont des ombres longues.
+narrateur|Victorino ferme le sac, lentement.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt pour demain.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. C'est du bon travail.
+maman|Tu as fini de fermer le sac ?
+enfant-m|Oui, maman.
+narrateur|Le sac bleu se pose près de la porte.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3570,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est près de la porte. Bravo, Victorino. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3710,10 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac est près de la porte.
+maman|Bravo, Victorino.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3741,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Le petit livre est sur la table. Une miette dort près de la couverture. Le livre, Victorino. C'est ce que j'ai dit. Victorino essuie une miette du doigt. Il met le livre dans le sac. Il est dedans, papa. Bravo. Tu as mis ce que l'adulte a dit. Les pages sont bien à l'abri ? Oui, maman. C'est du bon travail. Le sac bleu tient le livre contre la gourde.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,7 +3881,17 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Le petit livre est sur la table.
+narrateur|Une miette dort près de la couverture.
+papa|Le livre, Victorino. C'est ce que j'ai dit.
+narrateur|Victorino essuie une miette du doigt.
+narrateur|Il met le livre dans le sac.
+enfant-m|Il est dedans, papa.
+papa|Bravo. Tu as mis ce que l'adulte a dit.
+maman|Les pages sont bien à l'abri ?
+enfant-m|Oui, maman.
+maman|C'est du bon travail.
+narrateur|Le sac bleu tient le livre contre la gourde.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3994,7 +4111,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, le livre sent encore le papier neuf. Une tache de soleil touche la table. Victorino cale le livre dans le sac. Il ferme. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le livre est à l'abri. Bravo. Tu as fait du bon travail. On le laisse près du pain ? Près de la chaise, maman. Le sac bleu fait un petit ventre rond.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,7 +4251,17 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, le livre sent encore le papier neuf.
+narrateur|Une tache de soleil touche la table.
+narrateur|Victorino cale le livre dans le sac.
+narrateur|Il ferme. Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le livre est à l'abri.
+maman|Bravo. Tu as fait du bon travail.
+maman|On le laisse près du pain ?
+enfant-m|Près de la chaise, maman.
+narrateur|Le sac bleu fait un petit ventre rond.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4162,7 +4289,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le livre est dans le sac. Bravo. Tu as fait du bon travail. Le sac est prêt. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,7 +4429,10 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le livre est dans le sac.
+papa|Bravo. Tu as fait du bon travail.
+maman|Le sac est prêt.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4330,7 +4460,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pages sont tièdes. La cuisine sent encore le lait. Victorino glisse le livre, puis ferme. La fermeture chuchote zzz. Le sac est prêt. C'est ce que l'adulte a dit. Le livre est dedans. Bravo, Victorino. Tu veux un verre d'eau ? Oui, maman. L'eau fait un petit bruit dans le verre.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,7 +4600,17 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pages sont tièdes.
+narrateur|La cuisine sent encore le lait.
+narrateur|Victorino glisse le livre, puis ferme.
+narrateur|La fermeture chuchote zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Le livre est dedans.
+maman|Bravo, Victorino.
+maman|Tu veux un verre d'eau ?
+enfant-m|Oui, maman.
+narrateur|L'eau fait un petit bruit dans le verre.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4498,7 +4638,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai bu un peu d'eau. Bravo. Le sac tient ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,7 +4778,10 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai bu un peu d'eau.
+maman|Bravo.
+papa|Le sac tient ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4666,7 +4809,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, des miettes dorment sur la table. Le livre est déjà dans le sac. Victorino essuie une miette, puis ferme. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui. Le livre aussi. Bravo. C'est du bon travail. On éteint la lampe après ? Après, maman. Le sac attend dans l'ombre douce.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,7 +4949,17 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, des miettes dorment sur la table.
+narrateur|Le livre est déjà dans le sac.
+narrateur|Victorino essuie une miette, puis ferme.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui. Le livre aussi.
+maman|Bravo. C'est du bon travail.
+maman|On éteint la lampe après ?
+enfant-m|Après, maman.
+narrateur|Le sac attend dans l'ombre douce.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4834,7 +4987,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac attend dans l'ombre. Bravo, Victorino. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,7 +5127,10 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac attend dans l'ombre.
+papa|Bravo, Victorino.
+maman|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5002,7 +5158,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>Une petite tasse en bois attend. Elle est légère, presque chaude de soleil. La dînette, maman ! On joue un petit moment. Ensuite, on remet dans le sac ce que papa a dit. Victorino pose la tasse près du bol. Et la gourde ? Elle est dans le sac ? Oui, papa. Bravo. Le sac garde ce que j'ai dit. Tu as fini de poser la tasse ? Oui. Elle est à sa place.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,7 +5298,17 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Une petite tasse en bois attend.
+narrateur|Elle est légère, presque chaude de soleil.
+enfant-m|La dînette, maman !
+maman|On joue un petit moment.
+maman|Ensuite, on remet dans le sac ce que papa a dit.
+narrateur|Victorino pose la tasse près du bol.
+papa|Et la gourde ? Elle est dans le sac ?
+enfant-m|Oui, papa.
+papa|Bravo. Le sac garde ce que j'ai dit.
+maman|Tu as fini de poser la tasse ?
+enfant-m|Oui. Elle est à sa place.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5362,7 +5528,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, la petite tasse est encore à sa place. Ça sent le bol de maman. Victorino vérifie le sac, puis ferme. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. La gourde est dedans. Bravo. Tu as rangé la tasse aussi. Tu as fini le sac ? Oui, maman. Le bois de la tasse reste au soleil.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,7 +5668,17 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, la petite tasse est encore à sa place.
+narrateur|Ça sent le bol de maman.
+narrateur|Victorino vérifie le sac, puis ferme.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|La gourde est dedans.
+maman|Bravo. Tu as rangé la tasse aussi.
+maman|Tu as fini le sac ?
+enfant-m|Oui, maman.
+narrateur|Le bois de la tasse reste au soleil.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5530,7 +5706,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La tasse est à sa place. Bravo. Et le sac a ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,7 +5846,10 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La tasse est à sa place.
+maman|Bravo.
+papa|Et le sac a ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5698,7 +5877,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, la dînette est sage. La cuisine est un peu sombre, tout calme. Victorino pousse la fermeture. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Tout est dedans. Bravo, Victorino. On laisse la tasse sur la table ? Oui. À sa place. Le sac bleu fait un petit tas près du buffet.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,7 +6017,17 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, la dînette est sage.
+narrateur|La cuisine est un peu sombre, tout calme.
+narrateur|Victorino pousse la fermeture.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Tout est dedans.
+maman|Bravo, Victorino.
+maman|On laisse la tasse sur la table ?
+enfant-m|Oui. À sa place.
+narrateur|Le sac bleu fait un petit tas près du buffet.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5866,7 +6055,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est près du buffet. Bravo. C'est du bon travail. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,7 +6195,10 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac est près du buffet.
+papa|Bravo. C'est du bon travail.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6034,7 +6226,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, la petite assiette cliquette une fois. Puis plus rien. Victorino ferme le sac. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. Tu as fait du bon travail. On range la dînette pour la nuit ? Oui, maman. Le sac attend près de la porte de la cuisine.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,7 +6366,17 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, la petite assiette cliquette une fois.
+narrateur|Puis plus rien.
+narrateur|Victorino ferme le sac.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. Tu as fait du bon travail.
+maman|On range la dînette pour la nuit ?
+enfant-m|Oui, maman.
+narrateur|Le sac attend près de la porte de la cuisine.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6202,7 +6404,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La dînette est rangée. Bravo, Victorino. Le sac est prêt. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,7 +6544,10 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La dînette est rangée.
+maman|Bravo, Victorino.
+papa|Le sac est prêt.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6370,7 +6575,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le jardin. Ça sent le pain chaud. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Victorino porte le sac contre sa hanche. Il va vers le jardin. L'herbe est un peu humide. Un oiseau chante une fois. On reste près de la porte. Le sac vient avec nous. Le sac est un peu lourd. On met encore ce que j'ai dit. Papa tend le petit livre. Victorino le met dans le sac. Les pages froissent, tout bas. Tu as mis le livre ? Oui, maman. Bravo. C'est du bon travail. Le sac tient ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,8 +6715,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le jardin. Ça sent le pain chaud. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On attend son tour.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Victorino porte le sac contre sa hanche.
+narrateur|Il va vers le jardin.
+narrateur|L'herbe est un peu humide.
+narrateur|Un oiseau chante une fois.
+papa|On reste près de la porte.
+papa|Le sac vient avec nous.
+enfant-m|Le sac est un peu lourd.
+papa|On met encore ce que j'ai dit.
+narrateur|Papa tend le petit livre.
+narrateur|Victorino le met dans le sac.
+narrateur|Les pages froissent, tout bas.
+maman|Tu as mis le livre ?
+enfant-m|Oui, maman.
+maman|Bravo. C'est du bon travail.
+papa|Le sac tient ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6539,7 +6757,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Victorino prépare le sac. Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,7 +6917,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Victorino prépare le sac.
+narrateur|Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6727,7 +6946,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>Victorino pose la main sur le sac. Oui. On met ce que l'adulte a dit. Le livre est dans le sac. Bravo, Victorino. Le sac est déjà moins vide. Tu veux continuer ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,7 +7090,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>narrateur|Victorino pose la main sur le sac.
+papa|Oui. On met ce que l'adulte a dit.
+enfant-m|Le livre est dans le sac.
+maman|Bravo, Victorino.
+papa|Le sac est déjà moins vide.
+maman|Tu veux continuer ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -7091,7 +7316,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>Des cubes sont dans un panier, au soleil. Le vent est doux sur les mains. Les cubes restent dans le panier. Le sac prend ce que j'ai dit. Victorino range un cube qui a glissé. Il vérifie la gourde dans le sac. La gourde est là. Bravo. Tu regardes le sac. Tu as mis ce que papa a dit ? Oui, maman. On marche près de l'herbe. Tout doucement.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,7 +7456,17 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Des cubes sont dans un panier, au soleil.
+narrateur|Le vent est doux sur les mains.
+papa|Les cubes restent dans le panier.
+papa|Le sac prend ce que j'ai dit.
+narrateur|Victorino range un cube qui a glissé.
+narrateur|Il vérifie la gourde dans le sac.
+enfant-m|La gourde est là.
+maman|Bravo. Tu regardes le sac.
+maman|Tu as mis ce que papa a dit ?
+enfant-m|Oui, maman.
+papa|On marche près de l'herbe. Tout doucement.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7451,7 +7686,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, l'herbe a encore de la rosée. Les cubes brillent dans le panier. Victorino ferme le sac sur le pas de la porte. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. La gourde, le livre, le doudou. Bravo. C'est du bon travail. Tes mains sont un peu fraîches ? Un peu, maman. Un oiseau reprend une note, puis se tait.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,7 +7826,17 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'herbe a encore de la rosée.
+narrateur|Les cubes brillent dans le panier.
+narrateur|Victorino ferme le sac sur le pas de la porte.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|La gourde, le livre, le doudou.
+maman|Bravo. C'est du bon travail.
+maman|Tes mains sont un peu fraîches ?
+enfant-m|Un peu, maman.
+narrateur|Un oiseau reprend une note, puis se tait.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7619,7 +7864,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mes mains sont un peu fraîches. Bravo. Le sac est prêt. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,7 +8004,10 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mes mains sont un peu fraîches.
+maman|Bravo. Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7787,7 +8035,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, le jardin est tiède. Les cubes font de petites ombres. Victorino tire la fermeture. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui. Tout est dedans. Bravo, Victorino. On rentre le panier de cubes ? Oui, maman. Le sac bleu sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,7 +8175,17 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, le jardin est tiède.
+narrateur|Les cubes font de petites ombres.
+narrateur|Victorino tire la fermeture.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui. Tout est dedans.
+maman|Bravo, Victorino.
+maman|On rentre le panier de cubes ?
+enfant-m|Oui, maman.
+narrateur|Le sac bleu sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7955,7 +8213,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le panier rentre aussi. Bravo, Victorino. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,7 +8353,10 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le panier rentre aussi.
+papa|Bravo, Victorino.
+maman|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8123,7 +8384,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, le jardin devient bleu. Les cubes rentrent dans la maison. Victorino ferme le sac dans l'entrée. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. Tu as fait du bon travail. On essuie tes chaussures ? Elles font toc toc. Le sac attend sur le banc de l'entrée.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,7 +8524,17 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le jardin devient bleu.
+narrateur|Les cubes rentrent dans la maison.
+narrateur|Victorino ferme le sac dans l'entrée.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. Tu as fait du bon travail.
+maman|On essuie tes chaussures ?
+enfant-m|Elles font toc toc.
+narrateur|Le sac attend sur le banc de l'entrée.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8291,7 +8562,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mes chaussures font toc toc. Bravo. Le sac a ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,7 +8702,10 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mes chaussures font toc toc.
+maman|Bravo.
+papa|Le sac a ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8459,7 +8733,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Le petit livre chauffe un peu au soleil. Une feuille passe, toute légère. Le livre va dans le sac. C'est ce que l'adulte a dit. Victorino glisse le livre à côté de la gourde. Il est à l'abri, papa. Bravo. Tu as fait du bon travail. Les pages restent sèches ? Oui, maman. Dans le sac. Parfait. On reste ensemble. Le sac bleu sent un peu l'herbe.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,7 +8873,17 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Le petit livre chauffe un peu au soleil.
+narrateur|Une feuille passe, toute légère.
+papa|Le livre va dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Victorino glisse le livre à côté de la gourde.
+enfant-m|Il est à l'abri, papa.
+papa|Bravo. Tu as fait du bon travail.
+maman|Les pages restent sèches ?
+enfant-m|Oui, maman. Dans le sac.
+maman|Parfait. On reste ensemble.
+narrateur|Le sac bleu sent un peu l'herbe.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8819,7 +9103,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, le livre a pris un peu de soleil. Victorino le protège dans le sac. Il ferme. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le livre est au sec. Bravo. C'est du bon travail. Une feuille est restée sur le sac ? Je l'enlève, maman. La feuille vole vers l'herbe. Merci, Victorino.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,7 +9243,17 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, le livre a pris un peu de soleil.
+narrateur|Victorino le protège dans le sac.
+narrateur|Il ferme. Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le livre est au sec.
+maman|Bravo. C'est du bon travail.
+maman|Une feuille est restée sur le sac ?
+enfant-m|Je l'enlève, maman.
+narrateur|La feuille vole vers l'herbe.
+papa|Merci, Victorino.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8987,7 +9281,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La feuille est partie. Bravo. Le sac est prêt. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,7 +9421,10 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La feuille est partie.
+papa|Bravo. Le sac est prêt.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9155,7 +9452,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, le jardin est silencieux. Le livre est déjà dans le sac. Victorino ferme, tout doucement. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui, papa. Bravo, Victorino. On s'assoit une minute ? Sur le banc, maman. Le sac bleu repose entre papa et Victorino.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,7 +9592,17 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, le jardin est silencieux.
+narrateur|Le livre est déjà dans le sac.
+narrateur|Victorino ferme, tout doucement.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo, Victorino.
+maman|On s'assoit une minute ?
+enfant-m|Sur le banc, maman.
+narrateur|Le sac bleu repose entre papa et Victorino.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9323,7 +9630,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On s'est assis un peu. Bravo, Victorino. Le sac tient ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,7 +9770,10 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On s'est assis un peu.
+maman|Bravo, Victorino.
+papa|Le sac tient ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9491,7 +9801,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, un chat miaule une fois, au loin. Le livre est à l'abri. Victorino ferme le sac. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le livre est dedans. Bravo. Tu as fait du bon travail. On rentre le sac maintenant ? Oui, maman. Les chaussures font toc toc sur les dalles.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,7 +9941,17 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, un chat miaule une fois, au loin.
+narrateur|Le livre est à l'abri.
+narrateur|Victorino ferme le sac.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le livre est dedans.
+maman|Bravo. Tu as fait du bon travail.
+maman|On rentre le sac maintenant ?
+enfant-m|Oui, maman.
+narrateur|Les chaussures font toc toc sur les dalles.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9659,7 +9979,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On rentre le sac. Bravo. C'est du bon travail. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,7 +10119,10 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On rentre le sac.
+papa|Bravo. C'est du bon travail.
+maman|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9827,7 +10150,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>La petite dînette est sur le banc du jardin. Une tasse cliquette, tout bas. On pose la tasse. Puis le sac. Je pose la tasse. Victorino pose la tasse. Maintenant, le doudou dans le sac. Victorino met le doudou. C'est ce que j'ai dit. Bravo. Tu as mis ce que l'adulte a dit. Tu as fini le doudou ? Oui, papa. Il est dedans.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,7 +10290,17 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|La petite dînette est sur le banc du jardin.
+narrateur|Une tasse cliquette, tout bas.
+maman|On pose la tasse. Puis le sac.
+enfant-m|Je pose la tasse.
+narrateur|Victorino pose la tasse.
+papa|Maintenant, le doudou dans le sac.
+narrateur|Victorino met le doudou.
+papa|C'est ce que j'ai dit.
+maman|Bravo. Tu as mis ce que l'adulte a dit.
+papa|Tu as fini le doudou ?
+enfant-m|Oui, papa. Il est dedans.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10187,7 +10520,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, la petite tasse est froide. Victorino l'a laissée sur le banc. Il ferme le sac. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le doudou est dedans. Bravo. La tasse reste au jardin. Tu as fini le sac ? Oui, maman. Une abeille passe, tout haut, sans s'arrêter. On rentre le sac ensemble.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,7 +10660,17 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, la petite tasse est froide.
+narrateur|Victorino l'a laissée sur le banc.
+narrateur|Il ferme le sac. Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le doudou est dedans.
+maman|Bravo. La tasse reste au jardin.
+maman|Tu as fini le sac ?
+enfant-m|Oui, maman.
+narrateur|Une abeille passe, tout haut, sans s'arrêter.
+papa|On rentre le sac ensemble.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10355,7 +10698,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou est dans le sac. Bravo. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,7 +10838,10 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou est dans le sac.
+maman|Bravo.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10523,7 +10869,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, la dînette chauffe un peu. Victorino pose la tasse, puis ferme le sac. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui. Le doudou aussi. Bravo, Victorino. On laisse la dînette à l'ombre ? Oui, maman. Le sac bleu a un goût d'herbe, presque.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,7 +11009,16 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, la dînette chauffe un peu.
+narrateur|Victorino pose la tasse, puis ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui. Le doudou aussi.
+maman|Bravo, Victorino.
+maman|On laisse la dînette à l'ombre ?
+enfant-m|Oui, maman.
+narrateur|Le sac bleu a un goût d'herbe, presque.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10691,7 +11046,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La dînette reste à l'ombre. Bravo, Victorino. Le sac est prêt. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,7 +11186,10 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La dînette reste à l'ombre.
+papa|Bravo, Victorino.
+maman|Le sac est prêt.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10859,7 +11217,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, les chaussures font toc toc. La petite tasse rentre dans le panier. Victorino ferme le sac. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. C'est du bon travail. On rentre maintenant ? Avec le sac, maman. La porte du jardin cliquette, tout bas.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,7 +11357,17 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, les chaussures font toc toc.
+narrateur|La petite tasse rentre dans le panier.
+narrateur|Victorino ferme le sac.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. C'est du bon travail.
+maman|On rentre maintenant ?
+enfant-m|Avec le sac, maman.
+narrateur|La porte du jardin cliquette, tout bas.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11027,7 +11395,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La porte du jardin cliquette. Bravo. C'est du bon travail. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,7 +11535,10 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La porte du jardin cliquette.
+maman|Bravo. C'est du bon travail.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11195,7 +11566,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la chambre. Le vent est doux. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Victorino glisse le sac derrière lui. Il va vers la chambre. La couverture est douce sous la main. Le doudou attend sur l'oreiller. Tu vois le doudou ? Il est sur le lit, maman. On met le doudou. C'est ce que j'ai dit. Victorino prend le doudou. Il le met dans le sac. Le sac sent le savon, maintenant. Bravo, Victorino. Tu as mis ce que papa a dit ? Oui. Le doudou. Le sac se remplit. Doucement.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,8 +11706,20 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers la chambre. Le vent est doux. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On montre du doigt, sans courir.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Victorino glisse le sac derrière lui.
+narrateur|Il va vers la chambre.
+narrateur|La couverture est douce sous la main.
+narrateur|Le doudou attend sur l'oreiller.
+maman|Tu vois le doudou ?
+enfant-m|Il est sur le lit, maman.
+papa|On met le doudou. C'est ce que j'ai dit.
+narrateur|Victorino prend le doudou.
+narrateur|Il le met dans le sac.
+narrateur|Le sac sent le savon, maintenant.
+papa|Bravo, Victorino.
+maman|Tu as mis ce que papa a dit ?
+enfant-m|Oui. Le doudou.
+maman|Le sac se remplit. Doucement.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11364,7 +11747,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Victorino prépare le sac. Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11524,7 +11907,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Victorino prépare le sac.
+narrateur|Que met-on dans le sac ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11552,7 +11936,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>Victorino serre un peu la sangle. Oui. On met dans le sac ce que l'adulte a dit. Le doudou est dedans. Bravo. C'est du bon travail. Il reste le reste de la liste. On y va ensemble ? Oui, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11696,7 +12080,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Sami respire. Sami retient : sac, ce que l'adulte a dit. On continue, avec papa.</t>
+          <t>narrateur|Victorino serre un peu la sangle.
+papa|Oui. On met dans le sac ce que l'adulte a dit.
+enfant-m|Le doudou est dedans.
+maman|Bravo. C'est du bon travail.
+papa|Il reste le reste de la liste.
+maman|On y va ensemble ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11916,7 +12306,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>Des cubes sont au pied du lit. Un cube bleu touche le tapis. Les cubes restent au pied du lit. Le sac, lui, prend ce que j'ai dit. Victorino aligne deux cubes. Puis il pousse la gourde plus au fond. La gourde est bien, papa. Tu as mis ce que papa a dit ? Oui, maman. Bravo. Le sac se prépare. On parle tout bas, dans la chambre.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,7 +12446,17 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Des cubes sont au pied du lit.
+narrateur|Un cube bleu touche le tapis.
+papa|Les cubes restent au pied du lit.
+papa|Le sac, lui, prend ce que j'ai dit.
+narrateur|Victorino aligne deux cubes.
+narrateur|Puis il pousse la gourde plus au fond.
+enfant-m|La gourde est bien, papa.
+maman|Tu as mis ce que papa a dit ?
+enfant-m|Oui, maman.
+maman|Bravo. Le sac se prépare.
+papa|On parle tout bas, dans la chambre.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12276,7 +12676,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, la chambre sent le linge propre. Les cubes sont au pied du lit. Victorino ferme le sac sur le tapis. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. La gourde, le livre, le doudou. Bravo. Tu as fait du bon travail. On ouvre un peu le rideau ? Oui, maman. Un carré de lumière tombe sur le sac bleu.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,7 +12816,17 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, la chambre sent le linge propre.
+narrateur|Les cubes sont au pied du lit.
+narrateur|Victorino ferme le sac sur le tapis.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|La gourde, le livre, le doudou.
+maman|Bravo. Tu as fait du bon travail.
+maman|On ouvre un peu le rideau ?
+enfant-m|Oui, maman.
+narrateur|Un carré de lumière tombe sur le sac bleu.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12444,7 +12854,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le soleil est sur le sac. Bravo, Victorino. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,7 +12994,10 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le soleil est sur le sac.
+papa|Bravo, Victorino.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12612,7 +13025,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, l'oreiller est encore chaud. Les cubes n'ont pas bougé. Victorino tire la fermeture. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui, papa. Bravo, Victorino. Tu as encore sommeil ? Un tout petit peu. Le sac attend au pied de l'armoire.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,7 +13165,17 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, l'oreiller est encore chaud.
+narrateur|Les cubes n'ont pas bougé.
+narrateur|Victorino tire la fermeture.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo, Victorino.
+maman|Tu as encore sommeil ?
+enfant-m|Un tout petit peu.
+narrateur|Le sac attend au pied de l'armoire.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12780,7 +13203,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est près de l'armoire. Bravo. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,7 +13343,10 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac est près de l'armoire.
+maman|Bravo.
+papa|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12948,7 +13374,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, un chat miaule une fois, dehors. Les cubes rentrent dans leur boîte. Victorino ferme le sac. La fermeture fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. C'est du bon travail. On pose le sac près de la porte ? Oui, maman. La chambre redevient calme.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,7 +13514,17 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, un chat miaule une fois, dehors.
+narrateur|Les cubes rentrent dans leur boîte.
+narrateur|Victorino ferme le sac.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. C'est du bon travail.
+maman|On pose le sac près de la porte ?
+enfant-m|Oui, maman.
+narrateur|La chambre redevient calme.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13116,7 +13552,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La chambre est calme. Bravo. C'est du bon travail. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,7 +13692,10 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La chambre est calme.
+papa|Bravo. C'est du bon travail.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13284,7 +13723,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Le petit livre est sur la table de chevet. La lampe n'est pas allumée. Le livre, Victorino. On le met dans le sac. Victorino le prend à deux mains. Il le glisse contre le doudou. Le livre est avec le doudou. C'est ce que papa a dit ? Oui, maman. Bravo. Tu as fait du bon travail. Tu as fini le livre ? Il est dans le sac.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,7 +13863,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Le petit livre est sur la table de chevet.
+narrateur|La lampe n'est pas allumée.
+papa|Le livre, Victorino.
+papa|On le met dans le sac.
+narrateur|Victorino le prend à deux mains.
+narrateur|Il le glisse contre le doudou.
+enfant-m|Le livre est avec le doudou.
+maman|C'est ce que papa a dit ?
+enfant-m|Oui, maman.
+papa|Bravo. Tu as fait du bon travail.
+maman|Tu as fini le livre ?
+enfant-m|Il est dans le sac.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13644,7 +14094,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, le petit livre a dormi aussi. Victorino le glisse, puis ferme le sac. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le livre est avec le doudou. Bravo. Tu as fait du bon travail. On dit merci au livre ? Merci, petit livre. Merci, Victorino. Le sac bleu est rond, content.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,7 +14234,17 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, le petit livre a dormi aussi.
+narrateur|Victorino le glisse, puis ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le livre est avec le doudou.
+maman|Bravo. Tu as fait du bon travail.
+maman|On dit merci au livre ?
+enfant-m|Merci, petit livre.
+papa|Merci, Victorino.
+narrateur|Le sac bleu est rond, content.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13812,7 +14272,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, petit livre. Bravo, Victorino. Le sac a ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,7 +14412,10 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, petit livre.
+papa|Bravo, Victorino.
+maman|Le sac a ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13980,7 +14443,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pages sont un peu chaudes. Victorino ferme le sac contre le lit. La fermeture fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui. Le livre est dedans. Bravo, Victorino. On baisse un peu le store ? Oui, maman. La chambre redevient douce.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,7 +14583,16 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pages sont un peu chaudes.
+narrateur|Victorino ferme le sac contre le lit.
+narrateur|La fermeture fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui. Le livre est dedans.
+maman|Bravo, Victorino.
+maman|On baisse un peu le store ?
+enfant-m|Oui, maman.
+narrateur|La chambre redevient douce.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14148,7 +14620,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le store est un peu baissé. Bravo. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,7 +14760,10 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le store est un peu baissé.
+maman|Bravo.
+papa|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14316,7 +14791,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, les chaussures font toc toc dans l'entrée. Le livre est déjà dans le sac. Victorino ferme. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Oui, papa. Bravo. C'est du bon travail. On le pose pour demain ? Près de la porte, maman. La lampe de chevet s'éteint après.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,7 +14931,16 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, les chaussures font toc toc dans l'entrée.
+narrateur|Le livre est déjà dans le sac.
+narrateur|Victorino ferme. Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo. C'est du bon travail.
+maman|On le pose pour demain ?
+enfant-m|Près de la porte, maman.
+narrateur|La lampe de chevet s'éteint après.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14484,7 +14968,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est pour demain. Bravo. Tu as fait du bon travail. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,7 +15108,10 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac est pour demain.
+papa|Bravo. Tu as fait du bon travail.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14652,7 +15139,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>La dînette est dans un panier, près de l'armoire. Ça sent le bois. On range la petite assiette. Je la range, maman. Victorino pose l'assiette dans le panier. Et dans le sac, ce que j'ai dit. Victorino vérifie le doudou. Le doudou est dedans. Bravo. Le sac tient ce que l'adulte a dit. Tu as fini de ranger l'assiette ? Oui. Elle est dans le panier.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,7 +15279,17 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans le sac. Sami répète tout bas : sac, ce que l'adulte a dit. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|La dînette est dans un panier, près de l'armoire.
+narrateur|Ça sent le bois.
+maman|On range la petite assiette.
+enfant-m|Je la range, maman.
+narrateur|Victorino pose l'assiette dans le panier.
+papa|Et dans le sac, ce que j'ai dit.
+narrateur|Victorino vérifie le doudou.
+enfant-m|Le doudou est dedans.
+papa|Bravo. Le sac tient ce que l'adulte a dit.
+maman|Tu as fini de ranger l'assiette ?
+enfant-m|Oui. Elle est dans le panier.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -15012,7 +15509,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le matin, la dînette sent le bois. Victorino a rangé la petite assiette. Il ferme le sac. Ça fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. Le doudou est dedans. Bravo. Tu as fait du bon travail. Le panier de dînette est prêt aussi ? Oui, maman. Le sac bleu et le panier se regardent.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,7 +15649,16 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, la dînette sent le bois.
+narrateur|Victorino a rangé la petite assiette.
+narrateur|Il ferme le sac. Ça fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Le doudou est dedans.
+maman|Bravo. Tu as fait du bon travail.
+maman|Le panier de dînette est prêt aussi ?
+enfant-m|Oui, maman.
+narrateur|Le sac bleu et le panier se regardent.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15180,7 +15686,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le panier et le sac sont prêts. Bravo, Victorino. C'est ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +15826,10 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le panier et le sac sont prêts.
+maman|Bravo, Victorino.
+papa|C'est ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +15857,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les chaussures attendent. Elles feront toc toc plus tard. Victorino ferme le sac. Ça fait zzz. Le sac est prêt. C'est ce que l'adulte a dit. Oui, papa. Bravo, Victorino. On laisse la dînette dans le panier ? Oui. À sa place. La couverture retombe, toute douce.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +15997,17 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les chaussures attendent.
+narrateur|Elles feront toc toc plus tard.
+narrateur|Victorino ferme le sac.
+narrateur|Ça fait zzz.
+papa|Le sac est prêt.
+papa|C'est ce que l'adulte a dit.
+enfant-m|Oui, papa.
+maman|Bravo, Victorino.
+maman|On laisse la dînette dans le panier ?
+enfant-m|Oui. À sa place.
+narrateur|La couverture retombe, toute douce.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16035,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La dînette est dans le panier. Bravo. Tu as préparé le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16175,10 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La dînette est dans le panier.
+papa|Bravo.
+maman|Tu as préparé le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16206,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>Le soir, la couverture est déjà tirée. Victorino pose le sac au pied du lit. Il a fermé. Ça a fait zzz. Le sac est prêt. Tu as mis ce que l'adulte a dit. La gourde, le livre, le doudou. Bravo. Tu as fait du bon travail. On se dit bonne nuit après ? Après, maman. Le sac bleu veille, tout bas.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,7 +16346,16 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Préparer son sac. Voici le geste : mettre dans le sac. Sami a entendu : sac, ce que l'adulte a dit. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, la couverture est déjà tirée.
+narrateur|Victorino pose le sac au pied du lit.
+narrateur|Il a fermé. Ça a fait zzz.
+papa|Le sac est prêt.
+papa|Tu as mis ce que l'adulte a dit.
+enfant-m|La gourde, le livre, le doudou.
+maman|Bravo. Tu as fait du bon travail.
+maman|On se dit bonne nuit après ?
+enfant-m|Après, maman.
+narrateur|Le sac bleu veille, tout bas.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15852,7 +16383,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac veille près du lit. Bravo. C'est du bon travail. Tu as mis ce que l'adulte a dit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +16523,10 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le sac veille près du lit.
+maman|Bravo. C'est du bon travail.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +16548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +16586,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-009.xlsx
+++ b/stories/arbres/TREE-AUT-009.xlsx
@@ -2739,17 +2739,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, près du pain. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Une miette de matin colle à la dent dorée. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, près du pain.
 enfant-m|Ils ont une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -3108,17 +3108,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont attendu la sieste, au chaud. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède attend, sous la dent dorée. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont attendu la sieste, au chaud.
 enfant-m|Ils ont une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -3481,17 +3481,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, les cubes dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. La lampe allume un cube, derrière la dent. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3632,7 +3632,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, sous la lampe.
 enfant-m|Ils ont une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -4240,17 +4240,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, près du four. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page de matin sent le pain, au fond. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, près du four.
 enfant-m|Il a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -4609,17 +4609,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre fait un toit, sous le rideau. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a attendu le rideau, à plat.
 enfant-m|Il a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -4982,17 +4982,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, le livre dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, sous la lampe. Il a une place, le soir ! Le quai du tapis peut attendre dehors. La lampe glisse sur la couverture du livre. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, sous la lampe.
 enfant-m|Il a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -5741,17 +5741,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la cuisine, un peu lourd. Le matin, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, près du pain. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du matin sonne, toute petite. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5892,7 +5892,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, près du pain.
 enfant-m|Elle a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -6110,17 +6110,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la cuisine, un peu lourd. Après la sieste, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, sans rouler. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste ne roule plus. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a attendu, sans rouler.
 enfant-m|Elle a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -6483,17 +6483,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la cuisine, un peu lourd. Le soir, la tasse dans le sac ! Le pain a failli rester sur la chaise. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un reflet de lampe. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6634,7 +6634,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, sous la lampe.
 enfant-m|Elle a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -8000,17 +8000,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré l'herbe. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube d'herbe sèche, contre la dent dorée. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8151,7 +8151,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, malgré l'herbe.
 enfant-m|Ils ont une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -8369,17 +8369,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont séché, pendant la sieste. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube tiède sent la dalle, au fond. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont séché, pendant la sieste.
 enfant-m|Ils ont une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -8742,17 +8742,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, les cubes dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, malgré le soir. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde une poussière d'herbe. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8893,7 +8893,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, malgré le soir.
 enfant-m|Ils ont une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -9501,17 +9501,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le vent. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Une page d'air frais reste un peu froide. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9652,7 +9652,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, malgré le vent.
 enfant-m|Il a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu la dalle, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste sent la dalle chaude. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a attendu la dalle, à plat.
 enfant-m|Il a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -10243,17 +10243,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, le livre dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, malgré le portail. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir sent le portail, fermé. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10394,7 +10394,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, malgré le portail.
 enfant-m|Il a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -11002,17 +11002,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est près du jardin, un peu lourd. Le matin, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré la goutte. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du jardin sonne, au matin clair. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11153,7 +11153,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, malgré la goutte.
 enfant-m|Elle a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -11371,17 +11371,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est près du jardin, un peu lourd. Après la sieste, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a perdu sa goutte, au chaud. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste a perdu sa goutte. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11522,7 +11522,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a perdu sa goutte, au chaud.
 enfant-m|Elle a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -11744,17 +11744,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est près du jardin, un peu lourd. Le soir, la tasse dans le sac ! Le doudou a failli rester dans l'herbe. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, malgré le soir. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir reflète le portail. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11895,7 +11895,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, malgré le soir.
 enfant-m|Elle a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -13261,17 +13261,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, hors du lit. Ils ont une place, le matin ! Le quai du tapis peut attendre dehors. Un cube de lit brille, sous la dent dorée. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13412,7 +13412,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, hors du lit.
 enfant-m|Ils ont une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -13630,17 +13630,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont dormi, puis voyagé. Ils ont une place, après la sieste ! Le quai du tapis peut attendre dehors. Un cube de sieste dort, contre le doudou. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13781,7 +13781,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont dormi, puis voyagé.
 enfant-m|Ils ont une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -14003,17 +14003,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent de fermeture dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, les cubes dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino glisse un cube, puis l'autre, à plat. La dent dorée glisse, puis tient. Tes cubes ont une place, sous la lampe. Ils ont une place, le soir ! Le quai du tapis peut attendre dehors. Un cube du soir garde la poussière du lit. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14154,7 +14154,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino glisse un cube, puis l'autre, à plat.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Tes cubes ont une place, sous la lampe.
 enfant-m|Ils ont une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -14762,17 +14762,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors de l'oreiller. Il a une place, le matin ! Le quai du tapis peut attendre dehors. Le livre du matin sent l'oreiller, tiède. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14913,7 +14913,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, hors de l'oreiller.
 enfant-m|Il a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -15131,17 +15131,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a attendu le rideau, à plat. Il a une place, après la sieste ! Le quai du tapis peut attendre dehors. Le livre de sieste fait un toit, au lit. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15282,7 +15282,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a attendu le rideau, à plat.
 enfant-m|Il a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -15504,17 +15504,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent de fermeture dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, le livre dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino couche le livre, pages vers le fond. La dent dorée glisse, puis tient. Le livre a une place, hors du pli. Il a une place, le soir ! Le quai du tapis peut attendre dehors. Le livre du soir garde un pli d'oreiller. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15655,7 +15655,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino couche le livre, pages vers le fond.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|Le livre a une place, hors du pli.
 enfant-m|Il a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -16263,17 +16263,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair.</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair. [pause]</t>
+          <t>Au matin, la lumière est fraîche, près de la porte. Le sac bleu est dans la chambre, un peu lourd. Le matin, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, hors du drap. Elle a une place, le matin ! Le quai du tapis peut attendre dehors. La tasse du lit sonne, au matin clair. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16414,7 +16414,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, hors du drap.
 enfant-m|Elle a une place, le matin !
 maman|Le quai du tapis peut attendre dehors.
@@ -16632,17 +16632,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud.</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud. [pause]</t>
+          <t>Après la sieste, le rideau fait un carré chaud. Le sac bleu est dans la chambre, un peu lourd. Après la sieste, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a attendu, contre le doudou. Elle a une place, après la sieste ! Le quai du tapis peut attendre dehors. La tasse de sieste s'est nichée, au chaud. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16783,7 +16783,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a attendu, contre le doudou.
 enfant-m|Elle a une place, après la sieste !
 maman|Le quai du tapis peut attendre dehors.
@@ -17005,17 +17005,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe.</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la dent de fermeture dorée cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis level="moderate"&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent de fermeture dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe. [pause]</t>
+          <t>Le soir, la lampe allume le tapis, tout près. Le sac bleu est dans la chambre, un peu lourd. Le soir, la tasse dans le sac ! La sangle a failli rester sous le lit. Je ne force pas. Il s'arrête, et la &lt;emphasis&gt;dent de fermeture dorée&lt;/emphasis&gt; cligne. Victorino niche la tasse, contre le doudou. La dent dorée glisse, puis tient. La tasse a une place, sous la lampe. Elle a une place, le soir ! Le quai du tapis peut attendre dehors. La tasse du soir cache un rond de lampe. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17156,7 +17156,7 @@
 enfant-m|Je ne force pas.
 narrateur|Il s'arrête, et la dent de fermeture dorée cligne.
 narrateur|Victorino niche la tasse, contre le doudou.
-narrateur|La dent de fermeture dorée glisse, puis tient.
+narrateur|La dent dorée glisse, puis tient.
 papa|La tasse a une place, sous la lampe.
 enfant-m|Elle a une place, le soir !
 maman|Le quai du tapis peut attendre dehors.
@@ -17368,7 +17368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17425,6 +17425,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
